--- a/WorkBot/main/data/order_archive/Sysco/Sysco_Triphammer_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/Sysco/Sysco_Triphammer_20260724.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,6 +983,657 @@
         <v>83.14</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4579587</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" t="n">
+        <v>49.89</v>
+      </c>
+      <c r="E30" t="n">
+        <v>349.23</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5204383</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pan Spray</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="E31" t="n">
+        <v>41.18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2053722</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sauerkraut</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="E32" t="n">
+        <v>40.85</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0128298</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Soy Milk</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="E33" t="n">
+        <v>61.54</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1592336</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ham (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="E34" t="n">
+        <v>332.64</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7199860</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hard Boiled Egg</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="E35" t="n">
+        <v>116.55</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2366607</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Liquid Egg</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="E36" t="n">
+        <v>49.03</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9035601</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>American Cheese (Sliced)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="E37" t="n">
+        <v>89.98</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3830100</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Chicken Breast - Retail (Cooked)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>20</v>
+      </c>
+      <c r="D38" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1177.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4828802</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Heavy Cream</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>47.41</v>
+      </c>
+      <c r="E39" t="n">
+        <v>47.41</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4171902</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Manchego Cheese</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1073105</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mozz (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>104</v>
+      </c>
+      <c r="E41" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4066781</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Parmesan (Grated)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="E42" t="n">
+        <v>179.97</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6046902</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pork - Butt (Boneless)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1735372</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cucumber (English)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="E44" t="n">
+        <v>54.04</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2416691</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lettuce - Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="E45" t="n">
+        <v>110.25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1048313</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Lime - Fresh</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="E46" t="n">
+        <v>44.64</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1821529</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Onion - Shallot (Peeled)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>74.69</v>
+      </c>
+      <c r="E47" t="n">
+        <v>74.69</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>8337503</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Avocado - Hand Scooped</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="E48" t="n">
+        <v>170.97</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1956804</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Asiago (Shredded)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="E49" t="n">
+        <v>55.95</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7256054</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cheddar - Orange (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>38</v>
+      </c>
+      <c r="E50" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7456025</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Egg Patty - Whites</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="E51" t="n">
+        <v>37.13</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2536555</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Bacon (Pre-Cooked)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>15</v>
+      </c>
+      <c r="D52" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="E52" t="n">
+        <v>451.95</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7298333</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Beef - Ground</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1012327</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Blue Cheese (Crumbled)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>81.65000000000001</v>
+      </c>
+      <c r="E54" t="n">
+        <v>81.65000000000001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>7133036</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Chicken - Diced White &amp; Dark</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>12</v>
+      </c>
+      <c r="D55" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="E55" t="n">
+        <v>551.88</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>7917672</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Chicken Quarters</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="E56" t="n">
+        <v>98.75</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1145283</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chicken Thigh (Boneless)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>114.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2376067</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Falafel - Balls</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="E58" t="n">
+        <v>128.98</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>7836562</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Meat Ball All Beef</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>68.84999999999999</v>
+      </c>
+      <c r="E59" t="n">
+        <v>68.84999999999999</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7161191</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Vegan Mozz</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>89.65000000000001</v>
+      </c>
+      <c r="E60" t="n">
+        <v>179.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
